--- a/vse-loti/339307010/spec-339307010.xlsx
+++ b/vse-loti/339307010/spec-339307010.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -58,12 +61,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,14 +440,14 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,7 +511,7 @@
           <t>Труба стальная Тип 2</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>2.08</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -514,19 +520,19 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>78890.66</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>94668.78999999999</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>164092.57</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="3" t="n">
         <v>78890.66</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="3" t="n">
         <v>94668.78999999999</v>
       </c>
     </row>
@@ -539,7 +545,7 @@
           <t>Труба стальная Тип 3</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>1.44</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -548,19 +554,19 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
+      <c r="F3" s="3" t="n">
         <v>79281.35000000001</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="3" t="n">
         <v>95137.62</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="3" t="n">
         <v>114165.14</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="3" t="n">
         <v>79281.35000000001</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="3" t="n">
         <v>95137.62</v>
       </c>
     </row>
@@ -573,7 +579,7 @@
           <t>Труба стальная Тип 4</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="2" t="n">
         <v>2.57</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -582,19 +588,19 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
+      <c r="F4" s="3" t="n">
         <v>77158.88</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="3" t="n">
         <v>92590.66</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="3" t="n">
         <v>198298.32</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="3" t="n">
         <v>77158.88</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="3" t="n">
         <v>92590.66</v>
       </c>
     </row>
@@ -607,7 +613,7 @@
           <t>Труба стальная Тип 5</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="2" t="n">
         <v>9.109999999999999</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -616,19 +622,19 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
+      <c r="F5" s="3" t="n">
         <v>76239</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="3" t="n">
         <v>91486.8</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="3" t="n">
         <v>694537.29</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="3" t="n">
         <v>76239</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="3" t="n">
         <v>91486.8</v>
       </c>
     </row>
@@ -641,7 +647,7 @@
           <t>Труба стальная Тип 6</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="2" t="n">
         <v>2.48</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -650,19 +656,19 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
+      <c r="F6" s="3" t="n">
         <v>74178.07000000001</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="3" t="n">
         <v>89013.67999999999</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="3" t="n">
         <v>183961.61</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="3" t="n">
         <v>74178.07000000001</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="3" t="n">
         <v>89013.67999999999</v>
       </c>
     </row>
@@ -675,7 +681,7 @@
           <t>Труба стальная Тип 7</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="2" t="n">
         <v>1.24</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -684,19 +690,19 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
+      <c r="F7" s="3" t="n">
         <v>75093.07000000001</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="3" t="n">
         <v>90111.67999999999</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="3" t="n">
         <v>93115.41</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="3" t="n">
         <v>75093.07000000001</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="3" t="n">
         <v>90111.67999999999</v>
       </c>
     </row>
@@ -709,7 +715,7 @@
           <t>Труба стальная Тип 8</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="2" t="n">
         <v>0.79</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -718,19 +724,19 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
+      <c r="F8" s="3" t="n">
         <v>75599.03999999999</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="3" t="n">
         <v>90718.85000000001</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="3" t="n">
         <v>59723.24</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="3" t="n">
         <v>75599.03999999999</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="3" t="n">
         <v>90718.85000000001</v>
       </c>
     </row>
@@ -743,7 +749,7 @@
           <t>Труба стальная Тип 9</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="2" t="n">
         <v>0.28</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -752,19 +758,19 @@
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
+      <c r="F9" s="3" t="n">
         <v>99824.95</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="3" t="n">
         <v>119789.94</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="3" t="n">
         <v>27950.99</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="3" t="n">
         <v>99824.95</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="3" t="n">
         <v>119789.94</v>
       </c>
     </row>
@@ -777,7 +783,7 @@
           <t>Труба стальная Тип 10</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="2" t="n">
         <v>0.37</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -786,19 +792,19 @@
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="n">
+      <c r="F10" s="3" t="n">
         <v>99769.57000000001</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="3" t="n">
         <v>119723.48</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="3" t="n">
         <v>36914.74</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="3" t="n">
         <v>99769.57000000001</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="3" t="n">
         <v>119723.48</v>
       </c>
     </row>
@@ -811,7 +817,7 @@
           <t>Труба стальная Тип 11</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="2" t="n">
         <v>0.54</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -820,19 +826,19 @@
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="n">
+      <c r="F11" s="3" t="n">
         <v>95154.88</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="3" t="n">
         <v>114185.86</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="3" t="n">
         <v>51383.64</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="3" t="n">
         <v>95154.88</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="3" t="n">
         <v>114185.86</v>
       </c>
     </row>
@@ -845,7 +851,7 @@
           <t>Труба стальная Тип 1</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="2" t="n">
         <v>0.36</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -854,39 +860,39 @@
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="n">
+      <c r="F12" s="3" t="n">
         <v>78904.28</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="3" t="n">
         <v>94685.14</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="3" t="n">
         <v>28405.54</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="3" t="n">
         <v>78904.28</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="3" t="n">
         <v>94685.14</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H13" s="5" t="n">
         <v>1652548.49</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="5" t="n">
         <v>1653421</v>
       </c>
     </row>

--- a/vse-loti/339307010/spec-339307010.xlsx
+++ b/vse-loti/339307010/spec-339307010.xlsx
@@ -527,7 +527,7 @@
         <v>94668.78999999999</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>164092.57</v>
+        <v>164013.68</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>78890.66</v>
@@ -595,7 +595,7 @@
         <v>92590.66</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>198298.32</v>
+        <v>198144</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>77158.88</v>
@@ -663,7 +663,7 @@
         <v>89013.67999999999</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>183961.61</v>
+        <v>184184.15</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>74178.07000000001</v>
@@ -697,7 +697,7 @@
         <v>90111.67999999999</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>93115.41</v>
+        <v>93340.69</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>75093.07000000001</v>
@@ -731,7 +731,7 @@
         <v>90718.85000000001</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>59723.24</v>
+        <v>59572.04</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>75599.03999999999</v>
@@ -765,7 +765,7 @@
         <v>119789.94</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>27950.99</v>
+        <v>28350.29</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>99824.95</v>
@@ -799,7 +799,7 @@
         <v>119723.48</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>36914.74</v>
+        <v>37214.05</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>99769.57000000001</v>
@@ -833,7 +833,7 @@
         <v>114185.86</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>51383.64</v>
+        <v>51573.94</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>95154.88</v>
@@ -867,7 +867,7 @@
         <v>94685.14</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>28405.54</v>
+        <v>28326.64</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>78904.28</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>1652548.49</v>
+        <v>1653421.91</v>
       </c>
     </row>
     <row r="14">

--- a/vse-loti/339307010/spec-339307010.xlsx
+++ b/vse-loti/339307010/spec-339307010.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0.####"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -61,15 +62,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -446,8 +449,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,25 +479,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (без НДС)</t>
+          <t>Стоимость (без НДС)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (с НДС)</t>
+          <t>Цена за т (без НДС)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Стоимость (без НДС)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -519,20 +510,16 @@
           <t>Тонна; метрическая тонна (1000 кг)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="3" t="n">
+      <c r="E2" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>164013.68</v>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>78890.66</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>94668.78999999999</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>164013.68</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>78890.66</v>
-      </c>
-      <c r="J2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>94668.78999999999</v>
       </c>
     </row>
@@ -553,20 +540,16 @@
           <t>Тонна; метрическая тонна (1000 кг)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" s="3" t="n">
+      <c r="E3" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>114165.14</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>79281.35000000001</v>
       </c>
-      <c r="G3" s="3" t="n">
-        <v>95137.62</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>114165.14</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>79281.35000000001</v>
-      </c>
-      <c r="J3" s="3" t="n">
+      <c r="H3" s="4" t="n">
         <v>95137.62</v>
       </c>
     </row>
@@ -587,20 +570,16 @@
           <t>Тонна; метрическая тонна (1000 кг)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" s="3" t="n">
+      <c r="E4" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>198144</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>77158.88</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>92590.66</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>198144</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>77158.88</v>
-      </c>
-      <c r="J4" s="3" t="n">
+      <c r="H4" s="4" t="n">
         <v>92590.66</v>
       </c>
     </row>
@@ -621,20 +600,16 @@
           <t>Тонна; метрическая тонна (1000 кг)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" s="3" t="n">
+      <c r="E5" s="3" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>694537.29</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>76239</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>91486.8</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>694537.29</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>76239</v>
-      </c>
-      <c r="J5" s="3" t="n">
+      <c r="H5" s="4" t="n">
         <v>91486.8</v>
       </c>
     </row>
@@ -655,20 +630,16 @@
           <t>Тонна; метрическая тонна (1000 кг)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" s="3" t="n">
+      <c r="E6" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>184184.15</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>74178.07000000001</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>89013.67999999999</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>184184.15</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>74178.07000000001</v>
-      </c>
-      <c r="J6" s="3" t="n">
+      <c r="H6" s="4" t="n">
         <v>89013.67999999999</v>
       </c>
     </row>
@@ -689,20 +660,16 @@
           <t>Тонна; метрическая тонна (1000 кг)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" s="3" t="n">
+      <c r="E7" s="3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>93340.69</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>75093.07000000001</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>90111.67999999999</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>93340.69</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>75093.07000000001</v>
-      </c>
-      <c r="J7" s="3" t="n">
+      <c r="H7" s="4" t="n">
         <v>90111.67999999999</v>
       </c>
     </row>
@@ -723,20 +690,16 @@
           <t>Тонна; метрическая тонна (1000 кг)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" s="3" t="n">
+      <c r="E8" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>59572.04</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>75599.03999999999</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>90718.85000000001</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>59572.04</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>75599.03999999999</v>
-      </c>
-      <c r="J8" s="3" t="n">
+      <c r="H8" s="4" t="n">
         <v>90718.85000000001</v>
       </c>
     </row>
@@ -757,20 +720,16 @@
           <t>Тонна; метрическая тонна (1000 кг)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" s="3" t="n">
+      <c r="E9" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>28350.29</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>99824.95</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>119789.94</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>28350.29</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>99824.95</v>
-      </c>
-      <c r="J9" s="3" t="n">
+      <c r="H9" s="4" t="n">
         <v>119789.94</v>
       </c>
     </row>
@@ -791,20 +750,16 @@
           <t>Тонна; метрическая тонна (1000 кг)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" s="3" t="n">
+      <c r="E10" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>37214.05</v>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>99769.57000000001</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>119723.48</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>37214.05</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>99769.57000000001</v>
-      </c>
-      <c r="J10" s="3" t="n">
+      <c r="H10" s="4" t="n">
         <v>119723.48</v>
       </c>
     </row>
@@ -825,20 +780,16 @@
           <t>Тонна; метрическая тонна (1000 кг)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" s="3" t="n">
+      <c r="E11" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>51573.94</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>95154.88</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>114185.86</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>51573.94</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>95154.88</v>
-      </c>
-      <c r="J11" s="3" t="n">
+      <c r="H11" s="4" t="n">
         <v>114185.86</v>
       </c>
     </row>
@@ -859,40 +810,39 @@
           <t>Тонна; метрическая тонна (1000 кг)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" s="3" t="n">
+      <c r="E12" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>28326.64</v>
+      </c>
+      <c r="G12" s="4" t="n">
         <v>78904.28</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="H12" s="4" t="n">
         <v>94685.14</v>
       </c>
-      <c r="H12" s="3" t="n">
-        <v>28326.64</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>78904.28</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>94685.14</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="E13" s="6" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="F13" s="7" t="n">
         <v>1653421.91</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="F14" s="7" t="n">
         <v>1653421</v>
       </c>
     </row>

--- a/vse-loti/339307010/spec-339307010.xlsx
+++ b/vse-loti/339307010/spec-339307010.xlsx
@@ -16,12 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.####"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,12 +30,18 @@
     <font>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -46,7 +50,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00305496"/>
+        <fgColor rgb="FF305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,17 +71,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,17 +449,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,35 +471,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Наименование позиции (⌀ + s, если указано)</t>
+          <t>Наименование позиции</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>D×s, мм</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Кол-во (исх.)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Масса, т (приведённая)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -499,28 +516,33 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Труба стальная Тип 2</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Тонна; метрическая тонна (1000 кг)</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>164013.68</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>78890.66</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>94668.78999999999</v>
+          <t>Труба стальная водогазопроводная, ГОСТ 3262-75</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ду25×3.20</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>28326.64</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>78904.28</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>94685.14</v>
       </c>
     </row>
     <row r="3">
@@ -529,28 +551,33 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Труба стальная Тип 3</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Тонна; метрическая тонна (1000 кг)</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>114165.14</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>79281.35000000001</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>95137.62</v>
+          <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>∅57×3.50</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>164013.68</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>78890.66</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>94668.78999999999</v>
       </c>
     </row>
     <row r="4">
@@ -559,28 +586,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Труба стальная Тип 4</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Тонна; метрическая тонна (1000 кг)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>198144</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>77158.88</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>92590.66</v>
+          <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>∅76×3.50</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>114165.14</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>79281.35000000001</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>95137.62</v>
       </c>
     </row>
     <row r="5">
@@ -589,28 +621,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Труба стальная Тип 5</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Тонна; метрическая тонна (1000 кг)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>694537.29</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>76239</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>91486.8</v>
+          <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>∅89×3.50</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>198144</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>77158.88</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>92590.66</v>
       </c>
     </row>
     <row r="6">
@@ -619,28 +656,33 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Труба стальная Тип 6</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Тонна; метрическая тонна (1000 кг)</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>184184.15</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>74178.07000000001</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>89013.67999999999</v>
+          <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>∅108×4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>694537.29</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>76239</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>91486.8</v>
       </c>
     </row>
     <row r="7">
@@ -649,28 +691,33 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Труба стальная Тип 7</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Тонна; метрическая тонна (1000 кг)</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>93340.69</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>75093.07000000001</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>90111.67999999999</v>
+          <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>∅133×4.50</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>184184.15</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>74178.07000000001</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>89013.67999999999</v>
       </c>
     </row>
     <row r="8">
@@ -679,28 +726,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Труба стальная Тип 8</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Тонна; метрическая тонна (1000 кг)</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>59572.04</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>75599.03999999999</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>90718.85000000001</v>
+          <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>∅159×4.50</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>93340.69</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>75093.07000000001</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>90111.67999999999</v>
       </c>
     </row>
     <row r="9">
@@ -709,28 +761,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Труба стальная Тип 9</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Тонна; метрическая тонна (1000 кг)</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>28350.29</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>99824.95</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>119789.94</v>
+          <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>∅219×5</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>59572.04</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>75599.03999999999</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>90718.85000000001</v>
       </c>
     </row>
     <row r="10">
@@ -739,28 +796,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Труба стальная Тип 10</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Тонна; метрическая тонна (1000 кг)</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>37214.05</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>99769.57000000001</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>119723.48</v>
+          <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>∅325×6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>28350.29</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>99824.95</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>119789.94</v>
       </c>
     </row>
     <row r="11">
@@ -769,28 +831,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Труба стальная Тип 11</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Тонна; метрическая тонна (1000 кг)</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>51573.94</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>95154.88</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>114185.86</v>
+          <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>∅426×6</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>37214.05</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>99769.57000000001</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>119723.48</v>
       </c>
     </row>
     <row r="12">
@@ -799,57 +866,85 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Труба стальная Тип 1</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Тонна; метрическая тонна (1000 кг)</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>28326.64</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>78904.28</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>94685.14</v>
+          <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>∅530×7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>51573.94</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>95154.88</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>114185.86</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="6" t="n">
         <v>21.26</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="G13" s="7" t="n">
         <v>1653421.91</v>
       </c>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>НМЦК из обоснования:</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>1653421</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Источник: Обоснование НМЦК.doc</t>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>НМЦК (без НДС):</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>1653421.91</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>НМЦК (с НДС):</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>1984106.29</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Источник 1 (D, s, ГОСТ): Приложение Описание объекта закупки.doc</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Источник 2 (кол-во, цены): Обоснование НМЦК.doc</t>
         </is>
       </c>
     </row>

--- a/vse-loti/339307010/spec-339307010.xlsx
+++ b/vse-loti/339307010/spec-339307010.xlsx
@@ -71,10 +71,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,6 +86,7 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -494,17 +498,17 @@
           <t>Масса, т (приведённая)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Цена за т (без НДС)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -521,10 +525,10 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ду25×3.20</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
+          <t>25×3.20</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>0.36</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -532,16 +536,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>0.36</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="4" t="n">
         <v>28326.64</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>78904.28</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="4" t="n">
         <v>94685.14</v>
       </c>
     </row>
@@ -556,10 +560,10 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>∅57×3.50</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
+          <t>57×3.50</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>2.08</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -567,16 +571,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>2.08</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="4" t="n">
         <v>164013.68</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="4" t="n">
         <v>78890.66</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" s="4" t="n">
         <v>94668.78999999999</v>
       </c>
     </row>
@@ -591,10 +595,10 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>∅76×3.50</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
+          <t>76×3.50</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>1.44</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -602,16 +606,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <v>1.44</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="4" t="n">
         <v>114165.14</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="4" t="n">
         <v>79281.35000000001</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" s="4" t="n">
         <v>95137.62</v>
       </c>
     </row>
@@ -626,10 +630,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>∅89×3.50</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
+          <t>89×3.50</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>2.57</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -637,16 +641,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="3" t="n">
         <v>2.57</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="4" t="n">
         <v>198144</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="4" t="n">
         <v>77158.88</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" s="4" t="n">
         <v>92590.66</v>
       </c>
     </row>
@@ -661,10 +665,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>∅108×4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
+          <t>108×4</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>9.109999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -672,16 +676,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="4" t="n">
         <v>694537.29</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="4" t="n">
         <v>76239</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="4" t="n">
         <v>91486.8</v>
       </c>
     </row>
@@ -696,10 +700,10 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>∅133×4.50</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
+          <t>133×4.50</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>2.48</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -707,16 +711,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>2.48</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="4" t="n">
         <v>184184.15</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="4" t="n">
         <v>74178.07000000001</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" s="4" t="n">
         <v>89013.67999999999</v>
       </c>
     </row>
@@ -731,10 +735,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>∅159×4.50</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+          <t>159×4.50</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>1.24</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -742,16 +746,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="4" t="n">
         <v>93340.69</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="4" t="n">
         <v>75093.07000000001</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" s="4" t="n">
         <v>90111.67999999999</v>
       </c>
     </row>
@@ -766,10 +770,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>∅219×5</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
+          <t>219×5</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
         <v>0.79</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -777,16 +781,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>0.79</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="4" t="n">
         <v>59572.04</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="4" t="n">
         <v>75599.03999999999</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" s="4" t="n">
         <v>90718.85000000001</v>
       </c>
     </row>
@@ -801,10 +805,10 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>∅325×6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
+          <t>325×6</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
         <v>0.28</v>
       </c>
       <c r="E10" t="inlineStr">
@@ -812,16 +816,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="3" t="n">
         <v>0.28</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="4" t="n">
         <v>28350.29</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" s="4" t="n">
         <v>99824.95</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" s="4" t="n">
         <v>119789.94</v>
       </c>
     </row>
@@ -836,10 +840,10 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>∅426×6</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
+          <t>426×6</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
         <v>0.37</v>
       </c>
       <c r="E11" t="inlineStr">
@@ -847,16 +851,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="3" t="n">
         <v>0.37</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="4" t="n">
         <v>37214.05</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" s="4" t="n">
         <v>99769.57000000001</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" s="4" t="n">
         <v>119723.48</v>
       </c>
     </row>
@@ -871,10 +875,10 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>∅530×7</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
+          <t>530×7</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
         <v>0.54</v>
       </c>
       <c r="E12" t="inlineStr">
@@ -882,67 +886,67 @@
           <t>т</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="4" t="n">
         <v>51573.94</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="4" t="n">
         <v>95154.88</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" s="4" t="n">
         <v>114185.86</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="6" t="n">
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="7" t="n">
         <v>21.26</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="8" t="n">
         <v>1653421.91</v>
       </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>НМЦК (без НДС):</t>
         </is>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="4" t="n">
         <v>1653421.91</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>НМЦК (с НДС):</t>
         </is>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" s="10" t="n">
         <v>1984106.29</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Источник 1 (D, s, ГОСТ): Приложение Описание объекта закупки.doc</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Источник 2 (кол-во, цены): Обоснование НМЦК.doc</t>
         </is>

--- a/vse-loti/339307010/spec-339307010.xlsx
+++ b/vse-loti/339307010/spec-339307010.xlsx
@@ -71,13 +71,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -523,29 +529,29 @@
           <t>Труба стальная водогазопроводная, ГОСТ 3262-75</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>25×3.20</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.36</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
         <v>0.36</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="6" t="n">
         <v>28326.64</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="6" t="n">
         <v>78904.28</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="6" t="n">
         <v>94685.14</v>
       </c>
     </row>
@@ -558,29 +564,29 @@
           <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>57×3.50</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>2.08</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
         <v>2.08</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="6" t="n">
         <v>164013.68</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="6" t="n">
         <v>78890.66</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="6" t="n">
         <v>94668.78999999999</v>
       </c>
     </row>
@@ -593,29 +599,29 @@
           <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>76×3.50</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>1.44</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>1.44</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="6" t="n">
         <v>114165.14</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="6" t="n">
         <v>79281.35000000001</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="6" t="n">
         <v>95137.62</v>
       </c>
     </row>
@@ -628,29 +634,29 @@
           <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>89×3.50</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>2.57</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
         <v>2.57</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="6" t="n">
         <v>198144</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="6" t="n">
         <v>77158.88</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="6" t="n">
         <v>92590.66</v>
       </c>
     </row>
@@ -663,29 +669,29 @@
           <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>108×4</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="6" t="n">
         <v>694537.29</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="6" t="n">
         <v>76239</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="6" t="n">
         <v>91486.8</v>
       </c>
     </row>
@@ -698,29 +704,29 @@
           <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>133×4.50</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>2.48</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n">
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
         <v>2.48</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="6" t="n">
         <v>184184.15</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="6" t="n">
         <v>74178.07000000001</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="6" t="n">
         <v>89013.67999999999</v>
       </c>
     </row>
@@ -733,29 +739,29 @@
           <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>159×4.50</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>1.24</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
         <v>1.24</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="6" t="n">
         <v>93340.69</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="6" t="n">
         <v>75093.07000000001</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="6" t="n">
         <v>90111.67999999999</v>
       </c>
     </row>
@@ -768,29 +774,29 @@
           <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>219×5</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
         <v>0.79</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="6" t="n">
         <v>59572.04</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="6" t="n">
         <v>75599.03999999999</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="6" t="n">
         <v>90718.85000000001</v>
       </c>
     </row>
@@ -803,29 +809,29 @@
           <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>325×6</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>0.28</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>0.28</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="6" t="n">
         <v>28350.29</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="6" t="n">
         <v>99824.95</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I10" s="6" t="n">
         <v>119789.94</v>
       </c>
     </row>
@@ -838,29 +844,29 @@
           <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>426×6</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>0.37</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n">
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>0.37</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="6" t="n">
         <v>37214.05</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="6" t="n">
         <v>99769.57000000001</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="6" t="n">
         <v>119723.48</v>
       </c>
     </row>
@@ -873,80 +879,80 @@
           <t>Труба стальная электросварная прямошовная, ГОСТ 10704-91 / 10705-80</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>530×7</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>0.54</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>0.54</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="6" t="n">
         <v>51573.94</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="6" t="n">
         <v>95154.88</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" s="6" t="n">
         <v>114185.86</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="7" t="n">
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="9" t="n">
         <v>21.26</v>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="G13" s="10" t="n">
         <v>1653421.91</v>
       </c>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>НМЦК (без НДС):</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="6" t="n">
         <v>1653421.91</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>НМЦК (с НДС):</t>
         </is>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="G15" s="12" t="n">
         <v>1984106.29</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Источник 1 (D, s, ГОСТ): Приложение Описание объекта закупки.doc</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Источник 2 (кол-во, цены): Обоснование НМЦК.doc</t>
         </is>
